--- a/03_Outputs/Cartama/08_Educacion/educacion.xlsx
+++ b/03_Outputs/Cartama/08_Educacion/educacion.xlsx
@@ -5393,13 +5393,13 @@
         <v>2021</v>
       </c>
       <c r="F153" s="7">
-        <v>0.91188446869433</v>
+        <v>0.765811179416628</v>
       </c>
       <c r="G153" s="9">
-        <v>0.0331683157791443</v>
+        <v>0.0477489864144454</v>
       </c>
       <c r="H153" s="11">
-        <v>0.0510178295373343</v>
+        <v>0.0563272098948343</v>
       </c>
     </row>
     <row r="154">
@@ -5427,13 +5427,13 @@
         <v>2021</v>
       </c>
       <c r="F154" s="7">
-        <v>0.872001779366615</v>
+        <v>0.793502501294906</v>
       </c>
       <c r="G154" s="9">
-        <v>0.0186323709192612</v>
+        <v>0.0629997086090639</v>
       </c>
       <c r="H154" s="11">
-        <v>0.111149943064852</v>
+        <v>0.0713185398011997</v>
       </c>
     </row>
     <row r="155">
@@ -5461,13 +5461,13 @@
         <v>2021</v>
       </c>
       <c r="F155" s="7">
-        <v>0.808399619674067</v>
+        <v>0.924418856993982</v>
       </c>
       <c r="G155" s="9">
-        <v>0.0340611041845194</v>
+        <v>0.0471531226376282</v>
       </c>
       <c r="H155" s="11">
-        <v>0.0537186135094694</v>
+        <v>0.0582136438740334</v>
       </c>
     </row>
     <row r="156">
